--- a/Result/profitability/2543.xlsx
+++ b/Result/profitability/2543.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.22</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7824999999999999</v>
+        <v>0.7849999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>17.5025</v>
+        <v>17.62375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6562499999999999</v>
+        <v>0.5524999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>15.74875</v>
+        <v>14.1325</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.51</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4937499999999999</v>
+        <v>0.5299999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>11.75625</v>
+        <v>11.8525</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.28</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3724999999999999</v>
+        <v>0.4024999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>9.762499999999999</v>
+        <v>9.3825</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>0.13</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2962499999999999</v>
+        <v>0.33</v>
       </c>
       <c r="N6" t="n">
-        <v>8.06</v>
+        <v>7.76375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.51</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1437499999999999</v>
+        <v>0.17125</v>
       </c>
       <c r="N7" t="n">
-        <v>5.29625</v>
+        <v>5.40125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.09</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05999999999999994</v>
+        <v>0.13625</v>
       </c>
       <c r="N8" t="n">
-        <v>3.74625</v>
+        <v>4.3075</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>-1.79</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2100000000000001</v>
+        <v>-0.21</v>
       </c>
       <c r="N9" t="n">
         <v>-1.07125</v>
@@ -1772,7 +1772,7 @@
         <v>-0.06</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2150000000000001</v>
+        <v>-0.215</v>
       </c>
       <c r="N11" t="n">
         <v>-0.8937499999999996</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2543</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>4843</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3980</v>
+      </c>
+      <c r="E75" t="n">
+        <v>862</v>
+      </c>
+      <c r="F75" t="n">
+        <v>17.81</v>
+      </c>
+      <c r="G75" t="n">
+        <v>692</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>14.29%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-39</v>
+      </c>
+      <c r="J75" t="n">
+        <v>653</v>
+      </c>
+      <c r="K75" t="n">
+        <v>512</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.8774999999999998</v>
+      </c>
+      <c r="N75" t="n">
+        <v>19.21875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.648648648648649</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.489999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.337087087087087</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.3243243243243243</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.040000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1458033573141488</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
